--- a/UrbanEcho/UrbanEcho/Resources/Templates/templateSmall.xlsx
+++ b/UrbanEcho/UrbanEcho/Resources/Templates/templateSmall.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\courses\capstone\Project\Urban Traffic Sim\UrbanEcho\UrbanEcho\Resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2706B06-3AD5-43B1-AE09-CB9503D247E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327E565F-466D-424D-A9DD-BCC81E14B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Road Report" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Roads">'Road Report'!$A$8:$I$9</definedName>
+    <definedName name="Roads">'Road Report'!$A$8:$J$9</definedName>
     <definedName name="TheReport" localSheetId="1">'Intersections Report'!$A$6:$J$10</definedName>
     <definedName name="TheReport">#REF!</definedName>
     <definedName name="TheReport_Intersections" localSheetId="1">'Intersections Report'!$A$8:$J$9</definedName>
@@ -210,7 +210,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -222,96 +222,6 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="medium">
         <color auto="1"/>
@@ -340,12 +250,40 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -353,8 +291,36 @@
         <color auto="1"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -364,57 +330,32 @@
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -427,48 +368,58 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -747,52 +698,53 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="143.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="143.5703125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="31"/>
-      <c r="B2" s="32" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
     </row>
     <row r="4" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="31"/>
+      <c r="B4" s="7"/>
     </row>
     <row r="5" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A5" s="31"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
+      <c r="B9" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -808,104 +760,99 @@
   <dimension ref="B1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="2.28515625" style="17" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="2.85546875" style="17" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="41.42578125" style="17" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" style="17" customWidth="1"/>
-    <col min="6" max="6" width="27.5703125" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" style="17" customWidth="1"/>
-    <col min="8" max="8" width="24.42578125" style="17" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" style="17" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" style="17" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="1.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="2.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="2.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="4:10" s="18" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="26" t="s">
+    <row r="7" spans="4:10" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="I7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="4:10" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D8" s="19" t="s">
+    <row r="8" spans="4:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="28" t="s">
         <v>20</v>
       </c>
       <c r="J8" s="29" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="4:10" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="30"/>
-    </row>
-    <row r="10" spans="4:10" s="18" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="4:10" s="18" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="4:10" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="4:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="4:10" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -913,116 +860,114 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8D7773-B908-4AE1-8F78-AFB1C85B2E50}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="B1:J9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="4" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+    <row r="6" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:10" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="F7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="H7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="I7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="J7" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C8" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="D8" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="I8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="34" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12"/>
+    <row r="9" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/UrbanEcho/UrbanEcho/Resources/Templates/templateSmall.xlsx
+++ b/UrbanEcho/UrbanEcho/Resources/Templates/templateSmall.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\courses\capstone\Project\Urban Traffic Sim\UrbanEcho\UrbanEcho\Resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327E565F-466D-424D-A9DD-BCC81E14B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7B5D4B-862A-4C91-B418-4F0B351FA894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
     <t>CREATED Date {{Date}}</t>
   </si>
   <si>
-    <t>&lt;&lt;Image Value=MapImage Scale=2.0&gt;&gt;</t>
+    <t>&lt;&lt;Image Value=MapImage Scale=1.0&gt;&gt;</t>
   </si>
 </sst>
 </file>
